--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575159307</v>
+        <v>46157.93119315709</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119315709</v>
+        <v>46157.93185037458</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93185037458</v>
+        <v>46157.93406550236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406550236</v>
+        <v>46157.93724598884</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724598884</v>
+        <v>46158.2822228192</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822228192</v>
+        <v>46158.29706250839</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29706250839</v>
+        <v>46158.29822183177</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822183177</v>
+        <v>46158.33393228803</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393228803</v>
+        <v>46158.3686302123</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3686302123</v>
+        <v>46158.37293986174</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
